--- a/provident-system/server/uploads/templates/payroll.xlsx
+++ b/provident-system/server/uploads/templates/payroll.xlsx
@@ -1291,7 +1291,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A3:L33"/>
+  <dimension ref="A3:L42"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.64814814814815" customWidth="1"/>
@@ -1577,122 +1577,248 @@
       <c r="L23" s="9"/>
     </row>
     <row r="24" ht="15.6" customHeight="1" spans="1:12">
-      <c r="A24" s="28" t="s">
-        <v>14</v>
-      </c>
+      <c r="A24" s="28"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
-      <c r="G24" s="29">
-        <v>0</v>
-      </c>
+      <c r="G24" s="29"/>
       <c r="H24" s="28"/>
       <c r="I24" s="28"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
     </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="30" t="s">
+    <row r="25" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" ht="15.6" customHeight="1" spans="1:12">
+      <c r="A33" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="29">
+        <v>0</v>
+      </c>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="E35" s="31"/>
+      <c r="F35" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="34" t="s">
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="35" t="s">
+      <c r="B40" s="34"/>
+      <c r="C40" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="36" t="s">
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="37" t="s">
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37" t="s">
+      <c r="B41" s="37"/>
+      <c r="C41" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="37" t="s">
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-    </row>
-    <row r="33" spans="3:5">
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1702,15 +1828,15 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A26:B29"/>
-    <mergeCell ref="F26:I29"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="A35:B38"/>
+    <mergeCell ref="F35:I38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.15748031496063" bottom="0.15748031496063" header="0.31496062992126" footer="0.31496062992126"/>
